--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SunnyHoGaming\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFF0828-4CAF-48AD-B241-4843F254D010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B157768B-2D14-4F17-B622-641227DFC2E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28485" yWindow="1965" windowWidth="28185" windowHeight="12795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="450" yWindow="1125" windowWidth="28185" windowHeight="12795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Item" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="49">
   <si>
     <t>(name)</t>
   </si>
@@ -182,6 +182,38 @@
   </si>
   <si>
     <t>SoundPath</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 소지 개수</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStackCount</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이콘 경로</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>IconPath</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템 사용 타입</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseItemType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>OpenPopup</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reduce Hunger</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -189,7 +221,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -227,6 +259,13 @@
       <name val="Arial"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -268,7 +307,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -319,11 +358,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -384,6 +436,28 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -602,17 +676,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:S996"/>
+  <dimension ref="A1:V996"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" customWidth="1"/>
     <col min="3" max="3" width="51.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="33" customWidth="1"/>
-    <col min="9" max="9" width="30.5703125" customWidth="1"/>
+    <col min="4" max="10" width="33" customWidth="1"/>
+    <col min="12" max="12" width="30.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" customHeight="1">
+    <row r="1" spans="1:22" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -626,16 +700,25 @@
         <v>21</v>
       </c>
       <c r="E1" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="H1" s="18" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" ht="15.75" customHeight="1">
+      <c r="I1" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -652,11 +735,22 @@
         <v>11</v>
       </c>
       <c r="F2" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="25"/>
-    </row>
-    <row r="3" spans="1:19" ht="15.75" customHeight="1">
+      <c r="H2" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -670,16 +764,25 @@
         <v>7</v>
       </c>
       <c r="E3" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="G3" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="H3" s="19" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" ht="15.75" customHeight="1">
+      <c r="I3" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="15.75" customHeight="1">
       <c r="A4" s="5" t="s">
         <v>22</v>
       </c>
@@ -690,12 +793,16 @@
         <v>18</v>
       </c>
       <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
+      <c r="E4" s="21">
+        <v>1</v>
+      </c>
       <c r="F4" s="21"/>
       <c r="G4" s="21"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="21" t="s">
+        <v>47</v>
+      </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -705,8 +812,11 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
-    </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+    </row>
+    <row r="5" spans="1:22" ht="15.75" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>23</v>
       </c>
@@ -720,13 +830,17 @@
         <v>8</v>
       </c>
       <c r="E5" s="21">
+        <v>999</v>
+      </c>
+      <c r="F5" s="21">
         <v>-50</v>
       </c>
-      <c r="F5" s="21"/>
       <c r="G5" s="21"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="21" t="s">
+        <v>48</v>
+      </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
@@ -736,8 +850,11 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
-    </row>
-    <row r="6" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+    </row>
+    <row r="6" spans="1:22" ht="15.75" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>24</v>
       </c>
@@ -750,12 +867,14 @@
       <c r="D6" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="22">
+        <v>999</v>
+      </c>
       <c r="F6" s="22"/>
       <c r="G6" s="22"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="22"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -765,8 +884,11 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-    </row>
-    <row r="7" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+    </row>
+    <row r="7" spans="1:22" ht="15.75" customHeight="1">
       <c r="A7" s="6" t="s">
         <v>25</v>
       </c>
@@ -779,12 +901,14 @@
       <c r="D7" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="22"/>
+      <c r="E7" s="22">
+        <v>999</v>
+      </c>
       <c r="F7" s="22"/>
       <c r="G7" s="22"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="22"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
@@ -794,8 +918,11 @@
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-    </row>
-    <row r="8" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+    </row>
+    <row r="8" spans="1:22" ht="15.75" customHeight="1">
       <c r="A8" s="6" t="s">
         <v>26</v>
       </c>
@@ -808,12 +935,14 @@
       <c r="D8" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="21"/>
+      <c r="E8" s="21">
+        <v>999</v>
+      </c>
       <c r="F8" s="21"/>
       <c r="G8" s="21"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="21"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -823,8 +952,11 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
-    </row>
-    <row r="9" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+    </row>
+    <row r="9" spans="1:22" ht="15.75" customHeight="1">
       <c r="A9" s="6" t="s">
         <v>27</v>
       </c>
@@ -837,12 +969,14 @@
       <c r="D9" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="20"/>
+      <c r="E9" s="20">
+        <v>999</v>
+      </c>
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="20"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
@@ -852,8 +986,11 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
-    </row>
-    <row r="10" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+    </row>
+    <row r="10" spans="1:22" ht="15.75" customHeight="1">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="15"/>
@@ -861,9 +998,9 @@
       <c r="E10" s="22"/>
       <c r="F10" s="22"/>
       <c r="G10" s="22"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="22"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -873,8 +1010,11 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
-    </row>
-    <row r="11" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+    </row>
+    <row r="11" spans="1:22" ht="15.75" customHeight="1">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="15"/>
@@ -882,9 +1022,9 @@
       <c r="E11" s="22"/>
       <c r="F11" s="22"/>
       <c r="G11" s="22"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="22"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -894,8 +1034,11 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" ht="15.75" customHeight="1">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="16"/>
@@ -903,8 +1046,11 @@
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
       <c r="G12" s="23"/>
-    </row>
-    <row r="13" spans="1:19" ht="15.75" customHeight="1">
+      <c r="H12" s="23"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="23"/>
+    </row>
+    <row r="13" spans="1:22" ht="15.75" customHeight="1">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="17"/>
@@ -912,8 +1058,11 @@
       <c r="E13" s="24"/>
       <c r="F13" s="24"/>
       <c r="G13" s="24"/>
-    </row>
-    <row r="14" spans="1:19" ht="15.75" customHeight="1">
+      <c r="H13" s="24"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="24"/>
+    </row>
+    <row r="14" spans="1:22" ht="15.75" customHeight="1">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="17"/>
@@ -921,8 +1070,11 @@
       <c r="E14" s="24"/>
       <c r="F14" s="24"/>
       <c r="G14" s="24"/>
-    </row>
-    <row r="15" spans="1:19" ht="15.75" customHeight="1">
+      <c r="H14" s="24"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="24"/>
+    </row>
+    <row r="15" spans="1:22" ht="15.75" customHeight="1">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="17"/>
@@ -930,10 +1082,13 @@
       <c r="E15" s="24"/>
       <c r="F15" s="24"/>
       <c r="G15" s="24"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="1:19" ht="15.75" customHeight="1">
+      <c r="H15" s="24"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:22" ht="15.75" customHeight="1">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="17"/>
@@ -941,8 +1096,11 @@
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
       <c r="G16" s="24"/>
-    </row>
-    <row r="17" spans="1:9" ht="15.75" customHeight="1">
+      <c r="H16" s="24"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="24"/>
+    </row>
+    <row r="17" spans="1:12" ht="15.75" customHeight="1">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="17"/>
@@ -950,8 +1108,11 @@
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
-    </row>
-    <row r="18" spans="1:9" ht="15.75" customHeight="1">
+      <c r="H17" s="24"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="24"/>
+    </row>
+    <row r="18" spans="1:12" ht="15.75" customHeight="1">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="17"/>
@@ -959,8 +1120,11 @@
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
-    </row>
-    <row r="19" spans="1:9" ht="15.75" customHeight="1">
+      <c r="H18" s="24"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="24"/>
+    </row>
+    <row r="19" spans="1:12" ht="15.75" customHeight="1">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="17"/>
@@ -968,8 +1132,11 @@
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
       <c r="G19" s="24"/>
-    </row>
-    <row r="20" spans="1:9" ht="15.75" customHeight="1">
+      <c r="H19" s="24"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="24"/>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" customHeight="1">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="17"/>
@@ -977,8 +1144,11 @@
       <c r="E20" s="24"/>
       <c r="F20" s="24"/>
       <c r="G20" s="24"/>
-    </row>
-    <row r="21" spans="1:9" ht="15.75" customHeight="1">
+      <c r="H20" s="24"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="24"/>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" customHeight="1">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="17"/>
@@ -986,9 +1156,12 @@
       <c r="E21" s="24"/>
       <c r="F21" s="24"/>
       <c r="G21" s="24"/>
-      <c r="I21" s="3"/>
-    </row>
-    <row r="22" spans="1:9" ht="15.75" customHeight="1">
+      <c r="H21" s="24"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="24"/>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="1:12" ht="15.75" customHeight="1">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="26"/>
@@ -996,9 +1169,12 @@
       <c r="E22" s="28"/>
       <c r="F22" s="28"/>
       <c r="G22" s="28"/>
-      <c r="I22" s="3"/>
-    </row>
-    <row r="23" spans="1:9" ht="15.75" customHeight="1">
+      <c r="H22" s="28"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="28"/>
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" customHeight="1">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="26"/>
@@ -1006,9 +1182,12 @@
       <c r="E23" s="28"/>
       <c r="F23" s="28"/>
       <c r="G23" s="28"/>
-      <c r="I23" s="3"/>
-    </row>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1">
+      <c r="H23" s="28"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="28"/>
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" customHeight="1">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="26"/>
@@ -1016,9 +1195,12 @@
       <c r="E24" s="28"/>
       <c r="F24" s="28"/>
       <c r="G24" s="28"/>
-      <c r="I24" s="3"/>
-    </row>
-    <row r="25" spans="1:9" ht="15.75" customHeight="1">
+      <c r="H24" s="28"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="28"/>
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" customHeight="1">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="26"/>
@@ -1026,8 +1208,11 @@
       <c r="E25" s="28"/>
       <c r="F25" s="28"/>
       <c r="G25" s="28"/>
-    </row>
-    <row r="26" spans="1:9" ht="15.75" customHeight="1">
+      <c r="H25" s="28"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="28"/>
+    </row>
+    <row r="26" spans="1:12" ht="15.75" customHeight="1">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="26"/>
@@ -1035,8 +1220,11 @@
       <c r="E26" s="28"/>
       <c r="F26" s="28"/>
       <c r="G26" s="28"/>
-    </row>
-    <row r="27" spans="1:9" ht="15.75" customHeight="1">
+      <c r="H26" s="28"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="28"/>
+    </row>
+    <row r="27" spans="1:12" ht="15.75" customHeight="1">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="26"/>
@@ -1044,8 +1232,11 @@
       <c r="E27" s="28"/>
       <c r="F27" s="28"/>
       <c r="G27" s="28"/>
-    </row>
-    <row r="28" spans="1:9" ht="15.75" customHeight="1">
+      <c r="H27" s="28"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="28"/>
+    </row>
+    <row r="28" spans="1:12" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="27"/>
@@ -1053,8 +1244,11 @@
       <c r="E28" s="29"/>
       <c r="F28" s="29"/>
       <c r="G28" s="29"/>
-    </row>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1">
+      <c r="H28" s="29"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="29"/>
+    </row>
+    <row r="29" spans="1:12" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="27"/>
@@ -1062,8 +1256,11 @@
       <c r="E29" s="29"/>
       <c r="F29" s="29"/>
       <c r="G29" s="29"/>
-    </row>
-    <row r="30" spans="1:9" ht="15.75" customHeight="1">
+      <c r="H29" s="29"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="29"/>
+    </row>
+    <row r="30" spans="1:12" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="27"/>
@@ -1071,8 +1268,11 @@
       <c r="E30" s="29"/>
       <c r="F30" s="29"/>
       <c r="G30" s="29"/>
-    </row>
-    <row r="31" spans="1:9" ht="15.75" customHeight="1">
+      <c r="H30" s="29"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="29"/>
+    </row>
+    <row r="31" spans="1:12" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="10"/>
       <c r="C31" s="27"/>
@@ -1080,12 +1280,16 @@
       <c r="E31" s="29"/>
       <c r="F31" s="29"/>
       <c r="G31" s="29"/>
-    </row>
-    <row r="32" spans="1:9" ht="15.75" customHeight="1">
+      <c r="H31" s="29"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="29"/>
+    </row>
+    <row r="32" spans="1:12" ht="15.75" customHeight="1">
       <c r="D32" s="25"/>
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>
       <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
     </row>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SunnyHoGaming\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B157768B-2D14-4F17-B622-641227DFC2E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CD5826-B504-46E8-89EF-B6E91BD8F042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="450" yWindow="1125" windowWidth="28185" windowHeight="12795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="810" yWindow="1815" windowWidth="28185" windowHeight="12795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Item" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SunnyHoGaming\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CD5826-B504-46E8-89EF-B6E91BD8F042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44415B2C-CA44-4307-B2F3-14D329EE11C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="1815" windowWidth="28185" windowHeight="12795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Item" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="53">
   <si>
     <t>(name)</t>
   </si>
@@ -80,18 +80,10 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>프리팹 경로</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>사운드 경로</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>PrefabPath</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>숨겨진 노트</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -214,6 +206,29 @@
   </si>
   <si>
     <t>Reduce Hunger</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Food</t>
+  </si>
+  <si>
+    <t>Icon/Wire</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Plasma</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/LN</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Ice</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Note</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -307,7 +322,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -363,6 +378,19 @@
         <color indexed="64"/>
       </left>
       <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -436,8 +464,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -458,6 +484,8 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -676,17 +704,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:V996"/>
+  <dimension ref="A1:U996"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" customWidth="1"/>
     <col min="3" max="3" width="51.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="33" customWidth="1"/>
-    <col min="12" max="12" width="30.5703125" customWidth="1"/>
+    <col min="4" max="9" width="33" customWidth="1"/>
+    <col min="11" max="11" width="30.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="15.75" customHeight="1">
+    <row r="1" spans="1:21" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -697,10 +725,10 @@
         <v>5</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F1" s="18" t="s">
         <v>10</v>
@@ -708,17 +736,14 @@
       <c r="G1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="33" t="s">
+      <c r="H1" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" ht="15.75" customHeight="1">
+    </row>
+    <row r="2" spans="1:21" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -737,60 +762,54 @@
       <c r="F2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="30" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="I2" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="32" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" ht="15.75" customHeight="1">
+    </row>
+    <row r="3" spans="1:21" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F3" s="19" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>16</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>18</v>
       </c>
       <c r="D4" s="21"/>
       <c r="E4" s="21">
@@ -798,11 +817,13 @@
       </c>
       <c r="F4" s="21"/>
       <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="21" t="s">
-        <v>47</v>
-      </c>
+      <c r="H4" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -814,17 +835,16 @@
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
-    </row>
-    <row r="5" spans="1:22" ht="15.75" customHeight="1">
+    </row>
+    <row r="5" spans="1:21" ht="15.75" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>8</v>
@@ -836,11 +856,13 @@
         <v>-50</v>
       </c>
       <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="21" t="s">
-        <v>48</v>
-      </c>
+      <c r="H5" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
@@ -852,29 +874,30 @@
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-    </row>
-    <row r="6" spans="1:22" ht="15.75" customHeight="1">
+    </row>
+    <row r="6" spans="1:21" ht="15.75" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E6" s="22">
         <v>999</v>
       </c>
       <c r="F6" s="22"/>
       <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="22"/>
+      <c r="H6" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" s="22"/>
+      <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -886,29 +909,30 @@
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-    </row>
-    <row r="7" spans="1:22" ht="15.75" customHeight="1">
+    </row>
+    <row r="7" spans="1:21" ht="15.75" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E7" s="22">
         <v>999</v>
       </c>
       <c r="F7" s="22"/>
       <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="22"/>
+      <c r="H7" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" s="22"/>
+      <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
@@ -920,17 +944,16 @@
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-    </row>
-    <row r="8" spans="1:22" ht="15.75" customHeight="1">
+    </row>
+    <row r="8" spans="1:21" ht="15.75" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>13</v>
@@ -940,9 +963,11 @@
       </c>
       <c r="F8" s="21"/>
       <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="21"/>
+      <c r="H8" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="21"/>
+      <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -954,17 +979,16 @@
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-    </row>
-    <row r="9" spans="1:22" ht="15.75" customHeight="1">
+    </row>
+    <row r="9" spans="1:21" ht="15.75" customHeight="1">
       <c r="A9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="C9" s="13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>12</v>
@@ -974,9 +998,11 @@
       </c>
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="20"/>
+      <c r="H9" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="20"/>
+      <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
@@ -988,9 +1014,8 @@
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-    </row>
-    <row r="10" spans="1:22" ht="15.75" customHeight="1">
+    </row>
+    <row r="10" spans="1:21" ht="15.75" customHeight="1">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="15"/>
@@ -998,9 +1023,9 @@
       <c r="E10" s="22"/>
       <c r="F10" s="22"/>
       <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="22"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -1012,9 +1037,8 @@
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-    </row>
-    <row r="11" spans="1:22" ht="15.75" customHeight="1">
+    </row>
+    <row r="11" spans="1:21" ht="15.75" customHeight="1">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="15"/>
@@ -1022,9 +1046,9 @@
       <c r="E11" s="22"/>
       <c r="F11" s="22"/>
       <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="22"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -1036,9 +1060,8 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" ht="15.75" customHeight="1">
+    </row>
+    <row r="12" spans="1:21" ht="15.75" customHeight="1">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="16"/>
@@ -1046,11 +1069,10 @@
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
       <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="23"/>
-    </row>
-    <row r="13" spans="1:22" ht="15.75" customHeight="1">
+      <c r="H12" s="37"/>
+      <c r="I12" s="23"/>
+    </row>
+    <row r="13" spans="1:21" ht="15.75" customHeight="1">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="17"/>
@@ -1058,11 +1080,10 @@
       <c r="E13" s="24"/>
       <c r="F13" s="24"/>
       <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="24"/>
-    </row>
-    <row r="14" spans="1:22" ht="15.75" customHeight="1">
+      <c r="H13" s="38"/>
+      <c r="I13" s="24"/>
+    </row>
+    <row r="14" spans="1:21" ht="15.75" customHeight="1">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="17"/>
@@ -1070,11 +1091,10 @@
       <c r="E14" s="24"/>
       <c r="F14" s="24"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="24"/>
-    </row>
-    <row r="15" spans="1:22" ht="15.75" customHeight="1">
+      <c r="H14" s="38"/>
+      <c r="I14" s="24"/>
+    </row>
+    <row r="15" spans="1:21" ht="15.75" customHeight="1">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="17"/>
@@ -1082,13 +1102,12 @@
       <c r="E15" s="24"/>
       <c r="F15" s="24"/>
       <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="24"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:22" ht="15.75" customHeight="1">
+    </row>
+    <row r="16" spans="1:21" ht="15.75" customHeight="1">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="17"/>
@@ -1096,11 +1115,10 @@
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
       <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="24"/>
-    </row>
-    <row r="17" spans="1:12" ht="15.75" customHeight="1">
+      <c r="H16" s="38"/>
+      <c r="I16" s="24"/>
+    </row>
+    <row r="17" spans="1:11" ht="15.75" customHeight="1">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="17"/>
@@ -1108,11 +1126,10 @@
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="24"/>
-    </row>
-    <row r="18" spans="1:12" ht="15.75" customHeight="1">
+      <c r="H17" s="38"/>
+      <c r="I17" s="24"/>
+    </row>
+    <row r="18" spans="1:11" ht="15.75" customHeight="1">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="17"/>
@@ -1120,11 +1137,10 @@
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="24"/>
-    </row>
-    <row r="19" spans="1:12" ht="15.75" customHeight="1">
+      <c r="H18" s="38"/>
+      <c r="I18" s="24"/>
+    </row>
+    <row r="19" spans="1:11" ht="15.75" customHeight="1">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="17"/>
@@ -1132,11 +1148,10 @@
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
       <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="24"/>
-    </row>
-    <row r="20" spans="1:12" ht="15.75" customHeight="1">
+      <c r="H19" s="38"/>
+      <c r="I19" s="24"/>
+    </row>
+    <row r="20" spans="1:11" ht="15.75" customHeight="1">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="17"/>
@@ -1144,11 +1159,10 @@
       <c r="E20" s="24"/>
       <c r="F20" s="24"/>
       <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="24"/>
-    </row>
-    <row r="21" spans="1:12" ht="15.75" customHeight="1">
+      <c r="H20" s="38"/>
+      <c r="I20" s="24"/>
+    </row>
+    <row r="21" spans="1:11" ht="15.75" customHeight="1">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="17"/>
@@ -1156,12 +1170,11 @@
       <c r="E21" s="24"/>
       <c r="F21" s="24"/>
       <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="24"/>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="1:12" ht="15.75" customHeight="1">
+      <c r="H21" s="38"/>
+      <c r="I21" s="24"/>
+      <c r="K21" s="3"/>
+    </row>
+    <row r="22" spans="1:11" ht="15.75" customHeight="1">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="26"/>
@@ -1169,12 +1182,11 @@
       <c r="E22" s="28"/>
       <c r="F22" s="28"/>
       <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="28"/>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="1:12" ht="15.75" customHeight="1">
+      <c r="H22" s="39"/>
+      <c r="I22" s="28"/>
+      <c r="K22" s="3"/>
+    </row>
+    <row r="23" spans="1:11" ht="15.75" customHeight="1">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="26"/>
@@ -1182,12 +1194,11 @@
       <c r="E23" s="28"/>
       <c r="F23" s="28"/>
       <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="28"/>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="1:12" ht="15.75" customHeight="1">
+      <c r="H23" s="39"/>
+      <c r="I23" s="28"/>
+      <c r="K23" s="3"/>
+    </row>
+    <row r="24" spans="1:11" ht="15.75" customHeight="1">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="26"/>
@@ -1195,12 +1206,11 @@
       <c r="E24" s="28"/>
       <c r="F24" s="28"/>
       <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="41"/>
-      <c r="J24" s="28"/>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="1:12" ht="15.75" customHeight="1">
+      <c r="H24" s="39"/>
+      <c r="I24" s="28"/>
+      <c r="K24" s="3"/>
+    </row>
+    <row r="25" spans="1:11" ht="15.75" customHeight="1">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="26"/>
@@ -1209,10 +1219,9 @@
       <c r="F25" s="28"/>
       <c r="G25" s="28"/>
       <c r="H25" s="28"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="28"/>
-    </row>
-    <row r="26" spans="1:12" ht="15.75" customHeight="1">
+      <c r="I25" s="40"/>
+    </row>
+    <row r="26" spans="1:11" ht="15.75" customHeight="1">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="26"/>
@@ -1221,10 +1230,9 @@
       <c r="F26" s="28"/>
       <c r="G26" s="28"/>
       <c r="H26" s="28"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="28"/>
-    </row>
-    <row r="27" spans="1:12" ht="15.75" customHeight="1">
+      <c r="I26" s="40"/>
+    </row>
+    <row r="27" spans="1:11" ht="15.75" customHeight="1">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="26"/>
@@ -1233,10 +1241,9 @@
       <c r="F27" s="28"/>
       <c r="G27" s="28"/>
       <c r="H27" s="28"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="28"/>
-    </row>
-    <row r="28" spans="1:12" ht="15.75" customHeight="1">
+      <c r="I27" s="40"/>
+    </row>
+    <row r="28" spans="1:11" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="27"/>
@@ -1245,10 +1252,9 @@
       <c r="F28" s="29"/>
       <c r="G28" s="29"/>
       <c r="H28" s="29"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="29"/>
-    </row>
-    <row r="29" spans="1:12" ht="15.75" customHeight="1">
+      <c r="I28" s="41"/>
+    </row>
+    <row r="29" spans="1:11" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="27"/>
@@ -1257,10 +1263,9 @@
       <c r="F29" s="29"/>
       <c r="G29" s="29"/>
       <c r="H29" s="29"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="29"/>
-    </row>
-    <row r="30" spans="1:12" ht="15.75" customHeight="1">
+      <c r="I29" s="41"/>
+    </row>
+    <row r="30" spans="1:11" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="27"/>
@@ -1269,10 +1274,9 @@
       <c r="F30" s="29"/>
       <c r="G30" s="29"/>
       <c r="H30" s="29"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="29"/>
-    </row>
-    <row r="31" spans="1:12" ht="15.75" customHeight="1">
+      <c r="I30" s="41"/>
+    </row>
+    <row r="31" spans="1:11" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="10"/>
       <c r="C31" s="27"/>
@@ -1281,10 +1285,9 @@
       <c r="F31" s="29"/>
       <c r="G31" s="29"/>
       <c r="H31" s="29"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="29"/>
-    </row>
-    <row r="32" spans="1:12" ht="15.75" customHeight="1">
+      <c r="I31" s="41"/>
+    </row>
+    <row r="32" spans="1:11" ht="15.75" customHeight="1">
       <c r="D32" s="25"/>
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SunnyHoGaming\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44415B2C-CA44-4307-B2F3-14D329EE11C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68467A29-ECE9-4A6C-8E0C-D2AEB6E3CF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -209,26 +209,27 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>Icon/Wire</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Plasma</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/LN</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Ice</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Note</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>Icon/Food</t>
-  </si>
-  <si>
-    <t>Icon/Wire</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/Plasma</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/LN</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/Ice</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/Note</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -818,7 +819,7 @@
       <c r="F4" s="21"/>
       <c r="G4" s="21"/>
       <c r="H4" s="34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>45</v>
@@ -857,7 +858,7 @@
       </c>
       <c r="G5" s="21"/>
       <c r="H5" s="34" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I5" s="21" t="s">
         <v>46</v>
@@ -894,7 +895,7 @@
       <c r="F6" s="22"/>
       <c r="G6" s="22"/>
       <c r="H6" s="35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I6" s="22"/>
       <c r="J6" s="3"/>
@@ -929,7 +930,7 @@
       <c r="F7" s="22"/>
       <c r="G7" s="22"/>
       <c r="H7" s="35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I7" s="22"/>
       <c r="J7" s="3"/>
@@ -964,7 +965,7 @@
       <c r="F8" s="21"/>
       <c r="G8" s="21"/>
       <c r="H8" s="34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I8" s="21"/>
       <c r="J8" s="3"/>
@@ -999,7 +1000,7 @@
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
       <c r="H9" s="36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I9" s="20"/>
       <c r="J9" s="3"/>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SunnyHoGaming\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68467A29-ECE9-4A6C-8E0C-D2AEB6E3CF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C453FAB-1540-4C59-BABA-A8B5C12B0BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="405" yWindow="1260" windowWidth="28185" windowHeight="12795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Item" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
   <si>
     <t>(name)</t>
   </si>
@@ -201,10 +201,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>OpenPopup</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>Reduce Hunger</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -230,6 +226,42 @@
   </si>
   <si>
     <t>Icon/Food</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Photo_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>가족 사진</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>내가 지켜야할 가족들이다. 볼 때마다 힘이 난다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>OpenNotePopup</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Photo</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Phone_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>위성 전화기</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Phone</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>OpenPhonePopup</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -705,7 +737,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:U996"/>
+  <dimension ref="A1:U998"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
@@ -819,10 +851,10 @@
       <c r="F4" s="21"/>
       <c r="G4" s="21"/>
       <c r="H4" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -839,29 +871,23 @@
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>8</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="21">
-        <v>999</v>
-      </c>
-      <c r="F5" s="21">
-        <v>-50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F5" s="21"/>
       <c r="G5" s="21"/>
       <c r="H5" s="34" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -877,27 +903,25 @@
       <c r="U5" s="3"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="22">
-        <v>999</v>
-      </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="22"/>
+      <c r="A6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21">
+        <v>1</v>
+      </c>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="21"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -912,27 +936,31 @@
       <c r="U6" s="3"/>
     </row>
     <row r="7" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="22">
+      <c r="A7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="21">
         <v>999</v>
       </c>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="22"/>
+      <c r="F7" s="21">
+        <v>-50</v>
+      </c>
+      <c r="G7" s="21"/>
+      <c r="H7" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="21" t="s">
+        <v>45</v>
+      </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -948,26 +976,26 @@
     </row>
     <row r="8" spans="1:21" ht="15.75" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="21">
+        <v>22</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="22">
         <v>999</v>
       </c>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="34" t="s">
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="I8" s="21"/>
+      <c r="I8" s="22"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -983,26 +1011,26 @@
     </row>
     <row r="9" spans="1:21" ht="15.75" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="20">
+        <v>23</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="22">
         <v>999</v>
       </c>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="36" t="s">
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="20"/>
+      <c r="I9" s="22"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
@@ -1017,15 +1045,27 @@
       <c r="U9" s="3"/>
     </row>
     <row r="10" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="22"/>
+      <c r="A10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="21">
+        <v>999</v>
+      </c>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" s="21"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -1040,15 +1080,27 @@
       <c r="U10" s="3"/>
     </row>
     <row r="11" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="22"/>
+      <c r="A11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="20">
+        <v>999</v>
+      </c>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="20"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -1063,37 +1115,61 @@
       <c r="U11" s="3"/>
     </row>
     <row r="12" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="23"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
     </row>
     <row r="13" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="24"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
     </row>
     <row r="14" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="24"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="23"/>
     </row>
     <row r="15" spans="1:21" ht="15.75" customHeight="1">
       <c r="A15" s="8"/>
@@ -1105,8 +1181,6 @@
       <c r="G15" s="24"/>
       <c r="H15" s="38"/>
       <c r="I15" s="24"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
     </row>
     <row r="16" spans="1:21" ht="15.75" customHeight="1">
       <c r="A16" s="8"/>
@@ -1129,6 +1203,8 @@
       <c r="G17" s="24"/>
       <c r="H17" s="38"/>
       <c r="I17" s="24"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
     </row>
     <row r="18" spans="1:11" ht="15.75" customHeight="1">
       <c r="A18" s="8"/>
@@ -1173,30 +1249,28 @@
       <c r="G21" s="24"/>
       <c r="H21" s="38"/>
       <c r="I21" s="24"/>
-      <c r="K21" s="3"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="28"/>
-      <c r="K22" s="3"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="24"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="28"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="24"/>
       <c r="K23" s="3"/>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
@@ -1219,8 +1293,9 @@
       <c r="E25" s="28"/>
       <c r="F25" s="28"/>
       <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="40"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="28"/>
+      <c r="K25" s="3"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1">
       <c r="A26" s="9"/>
@@ -1230,8 +1305,9 @@
       <c r="E26" s="28"/>
       <c r="F26" s="28"/>
       <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="40"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="28"/>
+      <c r="K26" s="3"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1">
       <c r="A27" s="9"/>
@@ -1245,26 +1321,26 @@
       <c r="I27" s="40"/>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="41"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="40"/>
     </row>
     <row r="29" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="41"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="40"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
@@ -1289,28 +1365,48 @@
       <c r="I31" s="41"/>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1">
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="41"/>
+    </row>
+    <row r="33" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="41"/>
+    </row>
+    <row r="34" spans="1:9" ht="15.75" customHeight="1">
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+    </row>
+    <row r="35" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="36" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:9" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -2259,6 +2355,8 @@
     <row r="994" ht="15.75" customHeight="1"/>
     <row r="995" ht="15.75" customHeight="1"/>
     <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SunnyHoGaming\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C453FAB-1540-4C59-BABA-A8B5C12B0BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94A13AF-91B7-436C-B05E-2B449D34A04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="405" yWindow="1260" windowWidth="28185" windowHeight="12795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="62">
   <si>
     <t>(name)</t>
   </si>
@@ -262,6 +262,10 @@
   </si>
   <si>
     <t>OpenPhonePopup</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>지구와 통신할 수 있는 연락 수단이다. 무엇을 입력해야하는거지?</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -742,7 +746,7 @@
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="69.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="9" width="33" customWidth="1"/>
     <col min="11" max="11" width="30.5703125" customWidth="1"/>
   </cols>
@@ -876,7 +880,9 @@
       <c r="B5" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="14"/>
+      <c r="C5" s="14" t="s">
+        <v>61</v>
+      </c>
       <c r="D5" s="21"/>
       <c r="E5" s="21">
         <v>1</v>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SunnyHoGaming\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94A13AF-91B7-436C-B05E-2B449D34A04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C90381-D9C0-466F-8578-307E87C552F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="405" yWindow="1260" windowWidth="28185" windowHeight="12795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="285" yWindow="2235" windowWidth="28185" windowHeight="12795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Item" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
   <si>
     <t>(name)</t>
   </si>
@@ -266,6 +266,26 @@
   </si>
   <si>
     <t>지구와 통신할 수 있는 연락 수단이다. 무엇을 입력해야하는거지?</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Map_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>픽서 부르미</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>픽서들의 위치를 알 수 있고, 픽서들을 한 곳으로 모으는 장치이다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Map</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>OpenMapPopup</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -741,7 +761,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:U998"/>
+  <dimension ref="A1:U999"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
@@ -875,13 +895,13 @@
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="21">
@@ -890,10 +910,10 @@
       <c r="F5" s="21"/>
       <c r="G5" s="21"/>
       <c r="H5" s="34" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -910,13 +930,13 @@
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D6" s="21"/>
       <c r="E6" s="21">
@@ -925,9 +945,11 @@
       <c r="F6" s="21"/>
       <c r="G6" s="21"/>
       <c r="H6" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="I6" s="21"/>
+        <v>59</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -943,30 +965,24 @@
     </row>
     <row r="7" spans="1:21" ht="15.75" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>8</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="D7" s="21"/>
       <c r="E7" s="21">
-        <v>999</v>
-      </c>
-      <c r="F7" s="21">
-        <v>-50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F7" s="21"/>
       <c r="G7" s="21"/>
       <c r="H7" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="I7" s="21" t="s">
-        <v>45</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="I7" s="21"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -981,27 +997,31 @@
       <c r="U7" s="3"/>
     </row>
     <row r="8" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="22">
+      <c r="A8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="21">
         <v>999</v>
       </c>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="I8" s="22"/>
+      <c r="F8" s="21">
+        <v>20</v>
+      </c>
+      <c r="G8" s="21"/>
+      <c r="H8" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>45</v>
+      </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -1017,16 +1037,16 @@
     </row>
     <row r="9" spans="1:21" ht="15.75" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9" s="22">
         <v>999</v>
@@ -1034,7 +1054,7 @@
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
       <c r="H9" s="35" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="3"/>
@@ -1052,26 +1072,26 @@
     </row>
     <row r="10" spans="1:21" ht="15.75" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="21">
+        <v>23</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="22">
         <v>999</v>
       </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="21"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="22"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -1087,26 +1107,26 @@
     </row>
     <row r="11" spans="1:21" ht="15.75" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="20">
+        <v>24</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="21">
         <v>999</v>
       </c>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" s="20"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11" s="21"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -1121,15 +1141,27 @@
       <c r="U11" s="3"/>
     </row>
     <row r="12" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="22"/>
+      <c r="A12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="20">
+        <v>999</v>
+      </c>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" s="20"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -1167,26 +1199,38 @@
       <c r="U13" s="3"/>
     </row>
     <row r="14" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="23"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="3"/>
     </row>
     <row r="15" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="24"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="23"/>
     </row>
     <row r="16" spans="1:21" ht="15.75" customHeight="1">
       <c r="A16" s="8"/>
@@ -1209,8 +1253,6 @@
       <c r="G17" s="24"/>
       <c r="H17" s="38"/>
       <c r="I17" s="24"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
     </row>
     <row r="18" spans="1:11" ht="15.75" customHeight="1">
       <c r="A18" s="8"/>
@@ -1222,6 +1264,8 @@
       <c r="G18" s="24"/>
       <c r="H18" s="38"/>
       <c r="I18" s="24"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
     </row>
     <row r="19" spans="1:11" ht="15.75" customHeight="1">
       <c r="A19" s="8"/>
@@ -1277,18 +1321,17 @@
       <c r="G23" s="24"/>
       <c r="H23" s="38"/>
       <c r="I23" s="24"/>
-      <c r="K23" s="3"/>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="28"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="24"/>
       <c r="K24" s="3"/>
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1">
@@ -1323,8 +1366,9 @@
       <c r="E27" s="28"/>
       <c r="F27" s="28"/>
       <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="40"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="28"/>
+      <c r="K27" s="3"/>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1">
       <c r="A28" s="9"/>
@@ -1349,15 +1393,15 @@
       <c r="I29" s="40"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="41"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="40"/>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
@@ -1393,13 +1437,23 @@
       <c r="I33" s="41"/>
     </row>
     <row r="34" spans="1:9" ht="15.75" customHeight="1">
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-    </row>
-    <row r="35" spans="1:9" ht="15.75" customHeight="1"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="41"/>
+    </row>
+    <row r="35" spans="1:9" ht="15.75" customHeight="1">
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+    </row>
     <row r="36" spans="1:9" ht="15.75" customHeight="1"/>
     <row r="37" spans="1:9" ht="15.75" customHeight="1"/>
     <row r="38" spans="1:9" ht="15.75" customHeight="1"/>
@@ -2363,6 +2417,7 @@
     <row r="996" ht="15.75" customHeight="1"/>
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SunnyHoGaming\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C90381-D9C0-466F-8578-307E87C552F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CD8F88-751C-40A0-A323-D2E8F49D4820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="285" yWindow="2235" windowWidth="28185" windowHeight="12795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
